--- a/outputs/metrics/resultados_finales.xlsx
+++ b/outputs/metrics/resultados_finales.xlsx
@@ -4233,7 +4233,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>2026-10-21T06:34:08</t>
+          <t>2026-10-21T06:41:25</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="B358">
-        <f>============================= 7 passed in 3.08s ===============================</f>
+        <f>============================= 7 passed in 3.02s ===============================</f>
         <v/>
       </c>
     </row>

--- a/outputs/metrics/resultados_finales.xlsx
+++ b/outputs/metrics/resultados_finales.xlsx
@@ -4233,7 +4233,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>2026-10-21T06:41:25</t>
+          <t>2026-10-21T07:06:22</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="B358">
-        <f>============================= 7 passed in 3.02s ===============================</f>
+        <f>============================= 7 passed in 3.16s ===============================</f>
         <v/>
       </c>
     </row>
@@ -4254,7 +4254,11 @@
           <t>entorno.demo_url</t>
         </is>
       </c>
-      <c r="B359" t="inlineStr"/>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1DMhVk4nvT4OnvS_TD2CkKdzhl3Ulc-r3/view?usp=sharing</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -4262,7 +4266,11 @@
           <t>entorno.repo_url</t>
         </is>
       </c>
-      <c r="B360" t="inlineStr"/>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>https://github.com/atobarv/novar-reportes-ia</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
